--- a/assets/party_positions.xlsx
+++ b/assets/party_positions.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,30 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +56,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,319 +450,393 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Royal Chain Private Limited</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Royal Chain Limited</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RC-REFINISHING</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Reparing - Royal Chain Limited</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Aalishaan Jewels LLP</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AJ-REFINISHING</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Reparing-Aalishaan Jewels</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ARK CHAINS</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Reparing- ARK chains</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>REPARING-TITAN</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Aditya Birla - Novel Jewels</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Reparing-Aditya Birla - Novel Jewels</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MALABAR GOLD AND DIAMONDS LIMITED</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Reparing - Malabar Gold And Diamonds Limited</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>DVM AQUA GOLD PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Reparing-DVM Aqua Gold Private Limited</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>INDRAHEER GOLD</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Reparing-Indraheer  Gold</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>ADITYA FINDINGS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>SKY CHAINS &amp; JEWELLERY PVT LTD</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>ASTMANGAL CHAINS PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>K JEWEL COUTURE PRIVATE LIMITED</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>SHA UMMEDMAL TILOKCHANDJI</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>V-DIA JEWELS PRIVATE LIMITED</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ARK CHAINS</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DVM AQUA GOLD PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="B23" s="3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>V-DIA JEWELS PRIVATE LIMITED REPAIRING</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Kanakratna Exim PVT LTD</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>INDRAHEER GOLD</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ADITYA FINDINGS PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SKY CHAINS &amp; JEWELLERY PVT LTD</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ASTMANGAL CHAINS PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>RC-REFINISHING</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Reparing-Aditya Birla - Novel Jewels</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>K JEWEL COUTURE PRIVATE LIMITED</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SHA UMMEDMAL TILOKCHANDJI</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="B25" s="3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>QUALTIY ASSEY &amp; HALLMARKS LLP</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="B26" s="3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>ARIHANT-BULLION</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="B27" s="3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>MY CHAIN</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="B28" s="3" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Ankit</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="B29" s="3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>STAR-JEWELS</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="B30" s="3" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>SATISH LOBSTERS</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="B31" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Nikhil</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="B32" s="3" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>KALPLAXMI JEWELS PVT. LTD.</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="B33" s="3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>YAMUNA-BEADS</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="B34" s="3" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>MAURH-ENTERPRISES</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="B35" s="3" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>ABU-SAHABAJ</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="B36" s="3" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>CASH-SALE</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="B37" s="3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>SNEH-JAIN</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>30</v>
+      <c r="B38" s="3" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
